--- a/laporan_padel_dki_jakarta_2026-09-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-30.xlsx
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.959.000</t>
+          <t>Rp2.319.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.310.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.949.994</t>
+          <t>Rp2.824.994</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-30.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp523.000</t>
+          <t>Rp872.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp1.696.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.700.000</t>
+          <t>Rp12.250.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.475.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.796.000</t>
+          <t>Rp1.297.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.240.000</t>
+          <t>Rp9.340.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.670.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.075.004</t>
+          <t>Rp14.210.004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.112.000</t>
+          <t>Rp10.812.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp16.610.000</t>
+          <t>Rp16.785.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.697.000</t>
+          <t>Rp1.297.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.150.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp4.968.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp36.750.000</t>
+          <t>Rp37.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.665.000</t>
+          <t>Rp7.385.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.830.000</t>
+          <t>Rp6.070.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.435.000</t>
+          <t>Rp11.795.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp320.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.399.000</t>
+          <t>Rp6.199.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.990.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.185.000</t>
+          <t>Rp6.385.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp705.000</t>
+          <t>Rp995.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-30.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.395.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.536.000</t>
+          <t>Rp13.086.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.725.000</t>
+          <t>Rp14.375.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.340.000</t>
+          <t>Rp2.630.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp4.915.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.912.000</t>
+          <t>Rp7.488.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.145.000</t>
+          <t>Rp1.294.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.340.000</t>
+          <t>Rp9.780.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp260.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.820.000</t>
+          <t>Rp5.120.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp8.375.000</t>
+          <t>Rp7.395.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.210.004</t>
+          <t>Rp14.370.005</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.812.000</t>
+          <t>Rp12.212.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp2.840.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp6.330.000</t>
+          <t>Rp6.031.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>170</v>
       </c>
       <c r="D29" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp16.785.000</t>
+          <t>Rp17.685.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.297.000</t>
+          <t>Rp1.697.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.560.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp17.400.000</t>
+          <t>Rp18.900.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp9.750.000</t>
+          <t>Rp10.300.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>75</v>
       </c>
       <c r="D59" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp319.000</t>
+          <t>Rp213.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp3.045.000</t>
+          <t>Rp3.395.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp13.000.000</t>
+          <t>Rp12.550.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.317.500</t>
+          <t>Rp16.142.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp2.940.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp37.150.000</t>
+          <t>Rp38.350.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.615.000</t>
+          <t>Rp9.950.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.070.000</t>
+          <t>Rp5.280.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.265.000</t>
+          <t>Rp12.490.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp497.000</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.795.000</t>
+          <t>Rp11.975.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.825.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.864.000</t>
+          <t>Rp8.182.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.453.500</t>
+          <t>Rp19.218.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.664.000</t>
+          <t>Rp5.410.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp8.600.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.166.000</t>
+          <t>Rp6.558.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.015.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.315.000</t>
+          <t>Rp1.885.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.475.000</t>
+          <t>Rp13.575.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.775.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp16.425.000</t>
+          <t>Rp17.350.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp6.199.000</t>
+          <t>Rp7.799.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp28.400.000</t>
+          <t>Rp29.600.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp310.000</t>
+          <t>Rp465.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.650.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp2.345.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.744.500</t>
+          <t>Rp8.221.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.810.000</t>
+          <t>Rp22.830.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp3.570.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.899.988</t>
+          <t>Rp5.274.988</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.295.000</t>
+          <t>Rp2.695.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.930.000</t>
+          <t>Rp3.315.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.881.000</t>
+          <t>Rp1.931.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp3.490.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-30.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp872.000</t>
+          <t>Rp898.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.683.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.719.980</t>
+          <t>Rp7.370.981</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.175.000</t>
+          <t>Rp11.425.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.312.000</t>
+          <t>Rp1.888.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.476.000</t>
+          <t>Rp2.352.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.375.000</t>
+          <t>Rp14.925.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.600.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp825.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.630.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.910.000</t>
+          <t>Rp3.030.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.915.000</t>
+          <t>Rp5.165.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.220.000</t>
+          <t>Rp5.720.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp870.000</t>
+          <t>Rp2.130.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp1.170.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>180</v>
       </c>
       <c r="D44" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.156.000</t>
+          <t>Rp4.156.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.525.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp894.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp260.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp5.120.000</t>
+          <t>Rp5.705.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp7.395.000</t>
+          <t>Rp6.660.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.803.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp4.020.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp5.405.000</t>
+          <t>Rp5.585.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>68</v>
       </c>
       <c r="D97" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>28</v>
       </c>
       <c r="D98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.970.000</t>
+          <t>Rp6.120.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp12.100.000</t>
+          <t>Rp12.550.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp6.435.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp6.031.000</t>
+          <t>Rp6.380.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.697.000</t>
+          <t>Rp1.297.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.780.000</t>
+          <t>Rp5.780.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp6.225.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp4.968.000</t>
+          <t>Rp4.176.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp8.730.000</t>
+          <t>Rp9.390.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>75</v>
       </c>
       <c r="D59" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp213.000</t>
+          <t>Rp319.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.129.000</t>
+          <t>Rp7.317.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp38.350.000</t>
+          <t>Rp40.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.385.000</t>
+          <t>Rp6.885.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.319.000</t>
+          <t>Rp3.294.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.280.000</t>
+          <t>Rp6.070.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.070.000</t>
+          <t>Rp9.710.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6525,21 +6525,21 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp864.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp199.000</t>
+          <t>Rp50.000 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.975.000</t>
+          <t>Rp12.420.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.825.000</t>
+          <t>Rp7.175.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.218.500</t>
+          <t>Rp18.658.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.560.000</t>
+          <t>Rp9.330.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6866,11 +6866,11 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.900.000</t>
+          <t>Rp22.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp8.600.000</t>
+          <t>Rp9.300.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.558.000</t>
+          <t>Rp5.661.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp620.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.793.000</t>
+          <t>Rp6.343.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.470.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.885.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.575.000</t>
+          <t>Rp13.725.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.775.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp17.350.000</t>
+          <t>Rp18.050.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>56</v>
       </c>
       <c r="D42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp10.450.000</t>
+          <t>Rp10.725.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp29.600.000</t>
+          <t>Rp28.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp105.000 - Rp300.000</t>
+          <t>Rp75.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp465.000</t>
+          <t>Rp775.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.345.000</t>
+          <t>Rp2.715.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.435.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.824.994</t>
+          <t>Rp3.924.991</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp6.069.000</t>
+          <t>Rp5.419.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.830.000</t>
+          <t>Rp24.750.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp3.465.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.570.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp135.000 - Rp199.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.140.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.187.000</t>
+          <t>Rp3.832.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.053.000</t>
+          <t>Rp4.954.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.051.000</t>
+          <t>Rp2.727.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-30.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-30.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.683.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.440.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.760.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp5.585.000</t>
+          <t>Rp5.765.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>68</v>
       </c>
       <c r="D97" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp567.000</t>
+          <t>Rp648.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.124.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.142.500</t>
+          <t>Rp16.720.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.070.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.710.000</t>
+          <t>Rp11.110.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp864.000</t>
+          <t>Rp1.581.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.175.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.500.000</t>
+          <t>Rp22.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,21 +7300,21 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp145.000 - Rp275.000</t>
+          <t>Rp125.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.725.000</t>
+          <t>Rp14.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp434.000</t>
+          <t>Rp633.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp18.050.000</t>
+          <t>Rp18.275.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.221.500</t>
+          <t>Rp7.983.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp24.750.000</t>
+          <t>Rp24.450.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp100.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.954.000</t>
+          <t>Rp5.053.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.931.000</t>
+          <t>Rp2.129.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
